--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC50DFE0-17CF-2C4B-8C23-07C4111B994A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCC00F0-EF10-3042-AB37-AA9237DD0BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17840" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -86,7 +86,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> OO2594</t>
+    <t xml:space="preserve"> 002594</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -95,7 +95,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="0.0%"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -208,7 +208,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -224,7 +224,7 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -236,7 +236,10 @@
     <xf numFmtId="3" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -340,6 +343,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-1637-B548-8621-F340F3437B4E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -376,6 +384,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-1637-B548-8621-F340F3437B4E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -412,6 +425,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-1637-B548-8621-F340F3437B4E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:multiLvlStrRef>
@@ -423,7 +441,7 @@
                     <c:v>NVDA</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v> OO2594</c:v>
+                    <c:v> 002594</c:v>
                   </c:pt>
                   <c:pt idx="2">
                     <c:v>SPCX</c:v>
@@ -453,7 +471,7 @@
                   <c:v>2618</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15640</c:v>
+                  <c:v>16000</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1042</c:v>
@@ -505,6 +523,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-1637-B548-8621-F340F3437B4E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -541,6 +564,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-1637-B548-8621-F340F3437B4E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -577,6 +605,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-1637-B548-8621-F340F3437B4E}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:multiLvlStrRef>
@@ -588,7 +621,7 @@
                     <c:v>NVDA</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v> OO2594</c:v>
+                    <c:v> 002594</c:v>
                   </c:pt>
                   <c:pt idx="2">
                     <c:v>SPCX</c:v>
@@ -615,13 +648,13 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.13564766839378239</c:v>
+                  <c:v>0.13316378433367243</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8103626943005181</c:v>
+                  <c:v>0.81383519837232965</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.398963730569948E-2</c:v>
+                  <c:v>5.3001017293997962E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1619,22 +1652,22 @@
       </c>
       <c r="D2" s="5">
         <f>C2/C5</f>
-        <v>0.13564766839378239</v>
+        <v>0.13316378433367243</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="10" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="4">
-        <v>15640</v>
+        <v>16000</v>
       </c>
       <c r="D3" s="5">
         <f>C3/C5</f>
-        <v>0.8103626943005181</v>
+        <v>0.81383519837232965</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1649,7 +1682,7 @@
       </c>
       <c r="D4" s="5">
         <f>C4/C5</f>
-        <v>5.398963730569948E-2</v>
+        <v>5.3001017293997962E-2</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="17">
@@ -1659,7 +1692,7 @@
       <c r="B5" s="7"/>
       <c r="C5" s="8">
         <f>C2+C3+C4</f>
-        <v>19300</v>
+        <v>19660</v>
       </c>
       <c r="D5" s="9">
         <f>D2+D3+D4</f>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7DE259-F822-1D44-8BCD-A85A90BA3328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B69C40D-7759-254F-8F8A-828D93F863AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17840" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>比亚迪</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -103,6 +103,18 @@
   </si>
   <si>
     <t>GOOG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英伟达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泡泡玛特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HK9992</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -592,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE57C4F-471E-8541-927F-1BFCFB00BDB8}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:5" ht="17">
@@ -690,17 +702,17 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="4">
-        <v>5440</v>
+        <v>5374</v>
       </c>
       <c r="D10" s="5">
-        <f>C10/C14</f>
-        <v>0.20790338607353054</v>
+        <f>C10/C15</f>
+        <v>0.26141946782118014</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -711,11 +723,11 @@
         <v>10</v>
       </c>
       <c r="C11" s="4">
-        <v>16000</v>
+        <v>8690</v>
       </c>
       <c r="D11" s="5">
-        <f>C11/C14</f>
-        <v>0.61148054727508983</v>
+        <f>C11/C15</f>
+        <v>0.42272705161258939</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -726,39 +738,54 @@
         <v>14</v>
       </c>
       <c r="C12" s="4">
-        <v>2402</v>
+        <v>2433</v>
       </c>
       <c r="D12" s="5">
-        <f>C12/C14</f>
-        <v>9.1798517159672854E-2</v>
+        <f>C12/C15</f>
+        <v>0.118353845405458</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1918</v>
+      </c>
+      <c r="D13" s="5">
+        <f>C13/C15</f>
+        <v>9.3301551782847686E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="4">
-        <v>2324</v>
-      </c>
-      <c r="D13" s="5">
-        <f>C13/C14</f>
-        <v>8.8817549491706796E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="17">
-      <c r="A14" s="6" t="s">
+      <c r="C14" s="4">
+        <v>2142</v>
+      </c>
+      <c r="D14" s="5">
+        <f>C14/C15</f>
+        <v>0.1041980833779248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17">
+      <c r="A15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8">
-        <f>C10+C11+C12+C13</f>
-        <v>26166</v>
-      </c>
-      <c r="D14" s="9">
-        <f>D10+D11+D12+D13</f>
+      <c r="B15" s="7"/>
+      <c r="C15" s="8">
+        <f>C10+C11+C12+C13+C14</f>
+        <v>20557</v>
+      </c>
+      <c r="D15" s="9">
+        <f>D10+D11+D12+D13+D14</f>
         <v>1</v>
       </c>
     </row>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B69C40D-7759-254F-8F8A-828D93F863AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B9A177-3F59-8140-8266-4769B7AB8723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17840" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
@@ -708,11 +708,11 @@
         <v>8</v>
       </c>
       <c r="C10" s="4">
-        <v>5374</v>
+        <v>6541</v>
       </c>
       <c r="D10" s="5">
         <f>C10/C15</f>
-        <v>0.26141946782118014</v>
+        <v>0.30083245182357543</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -723,11 +723,11 @@
         <v>10</v>
       </c>
       <c r="C11" s="4">
-        <v>8690</v>
+        <v>8626</v>
       </c>
       <c r="D11" s="5">
         <f>C11/C15</f>
-        <v>0.42272705161258939</v>
+        <v>0.39672538288184706</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -738,11 +738,11 @@
         <v>14</v>
       </c>
       <c r="C12" s="4">
-        <v>2433</v>
+        <v>2509</v>
       </c>
       <c r="D12" s="5">
         <f>C12/C15</f>
-        <v>0.118353845405458</v>
+        <v>0.11539345996412638</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -753,11 +753,11 @@
         <v>17</v>
       </c>
       <c r="C13" s="4">
-        <v>1918</v>
+        <v>1952</v>
       </c>
       <c r="D13" s="5">
         <f>C13/C15</f>
-        <v>9.3301551782847686E-2</v>
+        <v>8.9776019868463411E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -768,11 +768,11 @@
         <v>9</v>
       </c>
       <c r="C14" s="4">
-        <v>2142</v>
+        <v>2115</v>
       </c>
       <c r="D14" s="5">
         <f>C14/C15</f>
-        <v>0.1041980833779248</v>
+        <v>9.7272685461987765E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="17">
@@ -782,11 +782,11 @@
       <c r="B15" s="7"/>
       <c r="C15" s="8">
         <f>C10+C11+C12+C13+C14</f>
-        <v>20557</v>
+        <v>21743</v>
       </c>
       <c r="D15" s="9">
         <f>D10+D11+D12+D13+D14</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02B9A177-3F59-8140-8266-4769B7AB8723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76E1E4B-B9E9-5C45-9ED3-781418A6F3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17840" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
@@ -708,11 +708,11 @@
         <v>8</v>
       </c>
       <c r="C10" s="4">
-        <v>6541</v>
+        <v>6936</v>
       </c>
       <c r="D10" s="5">
         <f>C10/C15</f>
-        <v>0.30083245182357543</v>
+        <v>0.29387340055927463</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -723,11 +723,11 @@
         <v>10</v>
       </c>
       <c r="C11" s="4">
-        <v>8626</v>
+        <v>8658</v>
       </c>
       <c r="D11" s="5">
         <f>C11/C15</f>
-        <v>0.39672538288184706</v>
+        <v>0.36683331921023643</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -742,7 +742,7 @@
       </c>
       <c r="D12" s="5">
         <f>C12/C15</f>
-        <v>0.11539345996412638</v>
+        <v>0.10630455046182527</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -753,11 +753,11 @@
         <v>17</v>
       </c>
       <c r="C13" s="4">
-        <v>1952</v>
+        <v>3483</v>
       </c>
       <c r="D13" s="5">
         <f>C13/C15</f>
-        <v>8.9776019868463411E-2</v>
+        <v>0.14757223964070842</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -768,11 +768,11 @@
         <v>9</v>
       </c>
       <c r="C14" s="4">
-        <v>2115</v>
+        <v>2016</v>
       </c>
       <c r="D14" s="5">
         <f>C14/C15</f>
-        <v>9.7272685461987765E-2</v>
+        <v>8.5416490127955255E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="17">
@@ -782,11 +782,11 @@
       <c r="B15" s="7"/>
       <c r="C15" s="8">
         <f>C10+C11+C12+C13+C14</f>
-        <v>21743</v>
+        <v>23602</v>
       </c>
       <c r="D15" s="9">
         <f>D10+D11+D12+D13+D14</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76E1E4B-B9E9-5C45-9ED3-781418A6F3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCEC672-0D78-7148-8E51-CFA1B962CCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17840" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17800" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>比亚迪</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,18 +94,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026Q3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>谷歌</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GOOG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>英伟达</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -115,6 +103,18 @@
   </si>
   <si>
     <t>HK9992</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可口可乐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>买入价</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -604,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE57C4F-471E-8541-927F-1BFCFB00BDB8}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:5" ht="17">
@@ -697,22 +697,22 @@
         <v>3</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" s="4">
-        <v>6936</v>
+        <v>6919</v>
       </c>
       <c r="D10" s="5">
-        <f>C10/C15</f>
-        <v>0.29387340055927463</v>
+        <f>C10/C14</f>
+        <v>0.28582641384723428</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -723,11 +723,11 @@
         <v>10</v>
       </c>
       <c r="C11" s="4">
-        <v>8658</v>
+        <v>9018</v>
       </c>
       <c r="D11" s="5">
-        <f>C11/C15</f>
-        <v>0.36683331921023643</v>
+        <f>C11/C14</f>
+        <v>0.3725368695005577</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -738,54 +738,39 @@
         <v>14</v>
       </c>
       <c r="C12" s="4">
-        <v>2509</v>
+        <v>4833</v>
       </c>
       <c r="D12" s="5">
-        <f>C12/C15</f>
-        <v>0.10630455046182527</v>
+        <f>C12/C14</f>
+        <v>0.19965299293592761</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>17</v>
-      </c>
       <c r="C13" s="4">
-        <v>3483</v>
+        <v>3437</v>
       </c>
       <c r="D13" s="5">
-        <f>C13/C15</f>
-        <v>0.14757223964070842</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="4">
-        <v>2016</v>
-      </c>
-      <c r="D14" s="5">
-        <f>C14/C15</f>
-        <v>8.5416490127955255E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="17">
-      <c r="A15" s="6" t="s">
+        <f>C13/C14</f>
+        <v>0.1419837237162804</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="17">
+      <c r="A14" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="8">
-        <f>C10+C11+C12+C13+C14</f>
-        <v>23602</v>
-      </c>
-      <c r="D15" s="9">
-        <f>D10+D11+D12+D13+D14</f>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8">
+        <f>C10+C11+C12+C13</f>
+        <v>24207</v>
+      </c>
+      <c r="D14" s="9">
+        <f>D10+D11+D12+D13</f>
         <v>1</v>
       </c>
     </row>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCEC672-0D78-7148-8E51-CFA1B962CCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927979C7-8DC5-B14E-B4AD-64429F85840A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17800" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
@@ -708,11 +708,11 @@
         <v>8</v>
       </c>
       <c r="C10" s="4">
-        <v>6919</v>
+        <v>7200</v>
       </c>
       <c r="D10" s="5">
         <f>C10/C14</f>
-        <v>0.28582641384723428</v>
+        <v>0.29114435907804287</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -723,11 +723,11 @@
         <v>10</v>
       </c>
       <c r="C11" s="4">
-        <v>9018</v>
+        <v>9260</v>
       </c>
       <c r="D11" s="5">
         <f>C11/C14</f>
-        <v>0.3725368695005577</v>
+        <v>0.37444399514759402</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -742,7 +742,7 @@
       </c>
       <c r="D12" s="5">
         <f>C12/C14</f>
-        <v>0.19965299293592761</v>
+        <v>0.19543065103113627</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -757,7 +757,7 @@
       </c>
       <c r="D13" s="5">
         <f>C13/C14</f>
-        <v>0.1419837237162804</v>
+        <v>0.13898099474322684</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17">
@@ -767,7 +767,7 @@
       <c r="B14" s="7"/>
       <c r="C14" s="8">
         <f>C10+C11+C12+C13</f>
-        <v>24207</v>
+        <v>24730</v>
       </c>
       <c r="D14" s="9">
         <f>D10+D11+D12+D13</f>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927979C7-8DC5-B14E-B4AD-64429F85840A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EECF62D-6E26-744A-B9D8-2115DB13009E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17800" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
@@ -712,7 +712,7 @@
       </c>
       <c r="D10" s="5">
         <f>C10/C14</f>
-        <v>0.29114435907804287</v>
+        <v>0.27028041593152896</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -727,7 +727,7 @@
       </c>
       <c r="D11" s="5">
         <f>C11/C14</f>
-        <v>0.37444399514759402</v>
+        <v>0.34761064604527198</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -738,11 +738,11 @@
         <v>14</v>
       </c>
       <c r="C12" s="4">
-        <v>4833</v>
+        <v>6742</v>
       </c>
       <c r="D12" s="5">
         <f>C12/C14</f>
-        <v>0.19543065103113627</v>
+        <v>0.25308757836255114</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -757,7 +757,7 @@
       </c>
       <c r="D13" s="5">
         <f>C13/C14</f>
-        <v>0.13898099474322684</v>
+        <v>0.12902135966064793</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17">
@@ -767,7 +767,7 @@
       <c r="B14" s="7"/>
       <c r="C14" s="8">
         <f>C10+C11+C12+C13</f>
-        <v>24730</v>
+        <v>26639</v>
       </c>
       <c r="D14" s="9">
         <f>D10+D11+D12+D13</f>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EECF62D-6E26-744A-B9D8-2115DB13009E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E5E2B0-02C6-D345-8837-5925F9D4A4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17800" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>比亚迪</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -604,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE57C4F-471E-8541-927F-1BFCFB00BDB8}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:5" ht="17">
@@ -708,69 +708,54 @@
         <v>8</v>
       </c>
       <c r="C10" s="4">
-        <v>7200</v>
+        <v>5494</v>
       </c>
       <c r="D10" s="5">
-        <f>C10/C14</f>
-        <v>0.27028041593152896</v>
+        <f>C10/C13</f>
+        <v>0.29273231031543051</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>9260</v>
+        <v>8256</v>
       </c>
       <c r="D11" s="5">
-        <f>C11/C14</f>
-        <v>0.34761064604527198</v>
+        <f>C11/C13</f>
+        <v>0.43989769820971869</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="C12" s="4">
-        <v>6742</v>
+        <v>5018</v>
       </c>
       <c r="D12" s="5">
-        <f>C12/C14</f>
-        <v>0.25308757836255114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="4">
-        <v>3437</v>
-      </c>
-      <c r="D13" s="5">
-        <f>C13/C14</f>
-        <v>0.12902135966064793</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="17">
-      <c r="A14" s="6" t="s">
+        <f>C12/C13</f>
+        <v>0.2673699914748508</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="17">
+      <c r="A13" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8">
-        <f>C10+C11+C12+C13</f>
-        <v>26639</v>
-      </c>
-      <c r="D14" s="9">
-        <f>D10+D11+D12+D13</f>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8">
+        <f>C10+C11+C12</f>
+        <v>18768</v>
+      </c>
+      <c r="D13" s="9">
+        <f>D10+D11+D12</f>
         <v>1</v>
       </c>
     </row>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E5E2B0-02C6-D345-8837-5925F9D4A4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA21EFB-5F05-A44F-85A5-8DA6AFBF30E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17800" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17760" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>比亚迪</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -115,6 +115,14 @@
   </si>
   <si>
     <t>买入价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>标普500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VOO</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -604,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE57C4F-471E-8541-927F-1BFCFB00BDB8}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:5" ht="17">
@@ -708,11 +716,11 @@
         <v>8</v>
       </c>
       <c r="C10" s="4">
-        <v>5494</v>
+        <v>4243</v>
       </c>
       <c r="D10" s="5">
-        <f>C10/C13</f>
-        <v>0.29273231031543051</v>
+        <f>C10/C14</f>
+        <v>0.20475822797027313</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -723,11 +731,11 @@
         <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>8256</v>
+        <v>6837</v>
       </c>
       <c r="D11" s="5">
-        <f>C11/C13</f>
-        <v>0.43989769820971869</v>
+        <f>C11/C14</f>
+        <v>0.32993919505839203</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -741,21 +749,36 @@
         <v>5018</v>
       </c>
       <c r="D12" s="5">
-        <f>C12/C13</f>
-        <v>0.2673699914748508</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="17">
-      <c r="A13" s="6" t="s">
+        <f>C12/C14</f>
+        <v>0.24215809284818068</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="4">
+        <v>4624</v>
+      </c>
+      <c r="D13" s="5">
+        <f>C13/C14</f>
+        <v>0.22314448412315413</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="17">
+      <c r="A14" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="8">
-        <f>C10+C11+C12</f>
-        <v>18768</v>
-      </c>
-      <c r="D13" s="9">
-        <f>D10+D11+D12</f>
+      <c r="B14" s="7"/>
+      <c r="C14" s="8">
+        <f>C10+C11+C12+C13</f>
+        <v>20722</v>
+      </c>
+      <c r="D14" s="9">
+        <f>D10+D11+D12+D13</f>
         <v>1</v>
       </c>
     </row>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA21EFB-5F05-A44F-85A5-8DA6AFBF30E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45176C0-8F79-EE4A-8289-72E4CC5D1536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17760" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
@@ -716,11 +716,11 @@
         <v>8</v>
       </c>
       <c r="C10" s="4">
-        <v>4243</v>
+        <v>3023.5</v>
       </c>
       <c r="D10" s="5">
         <f>C10/C14</f>
-        <v>0.20475822797027313</v>
+        <v>0.13935427373078607</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -731,11 +731,11 @@
         <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>6837</v>
+        <v>8006</v>
       </c>
       <c r="D11" s="5">
         <f>C11/C14</f>
-        <v>0.32993919505839203</v>
+        <v>0.36899960823174244</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -746,11 +746,11 @@
         <v>16</v>
       </c>
       <c r="C12" s="4">
-        <v>5018</v>
+        <v>5875</v>
       </c>
       <c r="D12" s="5">
         <f>C12/C14</f>
-        <v>0.24215809284818068</v>
+        <v>0.27078100154402784</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -761,11 +761,11 @@
         <v>19</v>
       </c>
       <c r="C13" s="4">
-        <v>4624</v>
+        <v>4792</v>
       </c>
       <c r="D13" s="5">
         <f>C13/C14</f>
-        <v>0.22314448412315413</v>
+        <v>0.22086511649344365</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17">
@@ -775,7 +775,7 @@
       <c r="B14" s="7"/>
       <c r="C14" s="8">
         <f>C10+C11+C12+C13</f>
-        <v>20722</v>
+        <v>21696.5</v>
       </c>
       <c r="D14" s="9">
         <f>D10+D11+D12+D13</f>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45176C0-8F79-EE4A-8289-72E4CC5D1536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BB7311-051B-0B47-9C48-0D64C6C6D571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17760" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
+    <workbookView xWindow="-20" yWindow="660" windowWidth="30240" windowHeight="17760" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>比亚迪</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -91,10 +91,6 @@
   </si>
   <si>
     <t>2026 Q2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>英伟达</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -612,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BE57C4F-471E-8541-927F-1BFCFB00BDB8}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:5" ht="17">
@@ -705,80 +701,65 @@
         <v>3</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
+      <c r="B10" s="10" t="s">
+        <v>13</v>
       </c>
       <c r="C10" s="4">
-        <v>3023.5</v>
+        <v>9108</v>
       </c>
       <c r="D10" s="5">
-        <f>C10/C14</f>
-        <v>0.13935427373078607</v>
+        <f>C10/C13</f>
+        <v>0.45960538931220668</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="10" t="s">
         <v>14</v>
       </c>
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="C11" s="4">
-        <v>8006</v>
+        <v>5909</v>
       </c>
       <c r="D11" s="5">
-        <f>C11/C14</f>
-        <v>0.36899960823174244</v>
+        <f>C11/C13</f>
+        <v>0.29817833173537872</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" s="4">
-        <v>5875</v>
+        <v>4800</v>
       </c>
       <c r="D12" s="5">
-        <f>C12/C14</f>
-        <v>0.27078100154402784</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="4">
-        <v>4792</v>
-      </c>
-      <c r="D13" s="5">
-        <f>C13/C14</f>
-        <v>0.22086511649344365</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="17">
-      <c r="A14" s="6" t="s">
+        <f>C12/C13</f>
+        <v>0.2422162789524146</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="17">
+      <c r="A13" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="8">
-        <f>C10+C11+C12+C13</f>
-        <v>21696.5</v>
-      </c>
-      <c r="D14" s="9">
-        <f>D10+D11+D12+D13</f>
+      <c r="B13" s="7"/>
+      <c r="C13" s="8">
+        <f>C10+C11+C12</f>
+        <v>19817</v>
+      </c>
+      <c r="D13" s="9">
+        <f>D10+D11+D12</f>
         <v>1</v>
       </c>
     </row>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03BB7311-051B-0B47-9C48-0D64C6C6D571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A7148F-0AAF-CA4D-AD83-5D1B32F14CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="660" windowWidth="30240" windowHeight="17760" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17760" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -712,11 +712,11 @@
         <v>13</v>
       </c>
       <c r="C10" s="4">
-        <v>9108</v>
+        <v>9361</v>
       </c>
       <c r="D10" s="5">
         <f>C10/C13</f>
-        <v>0.45960538931220668</v>
+        <v>0.46826071732279528</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -727,11 +727,11 @@
         <v>15</v>
       </c>
       <c r="C11" s="4">
-        <v>5909</v>
+        <v>5844</v>
       </c>
       <c r="D11" s="5">
         <f>C11/C13</f>
-        <v>0.29817833173537872</v>
+        <v>0.29233154919713872</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -742,11 +742,11 @@
         <v>18</v>
       </c>
       <c r="C12" s="4">
-        <v>4800</v>
+        <v>4786</v>
       </c>
       <c r="D12" s="5">
         <f>C12/C13</f>
-        <v>0.2422162789524146</v>
+        <v>0.23940773348006603</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="17">
@@ -756,7 +756,7 @@
       <c r="B13" s="7"/>
       <c r="C13" s="8">
         <f>C10+C11+C12</f>
-        <v>19817</v>
+        <v>19991</v>
       </c>
       <c r="D13" s="9">
         <f>D10+D11+D12</f>

--- a/my_invest.xlsx
+++ b/my_invest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yueming/startup/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A7148F-0AAF-CA4D-AD83-5D1B32F14CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A37781-0CD7-C048-80A3-22A2631A3D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17760" xr2:uid="{E36D4951-2026-884A-BD31-41528F7E8D91}"/>
   </bookViews>
@@ -716,7 +716,7 @@
       </c>
       <c r="D10" s="5">
         <f>C10/C13</f>
-        <v>0.46826071732279528</v>
+        <v>0.37680634383931089</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -731,7 +731,7 @@
       </c>
       <c r="D11" s="5">
         <f>C11/C13</f>
-        <v>0.29233154919713872</v>
+        <v>0.23523729018234513</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -742,11 +742,11 @@
         <v>18</v>
       </c>
       <c r="C12" s="4">
-        <v>4786</v>
+        <v>9638</v>
       </c>
       <c r="D12" s="5">
         <f>C12/C13</f>
-        <v>0.23940773348006603</v>
+        <v>0.38795636597834399</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="17">
@@ -756,7 +756,7 @@
       <c r="B13" s="7"/>
       <c r="C13" s="8">
         <f>C10+C11+C12</f>
-        <v>19991</v>
+        <v>24843</v>
       </c>
       <c r="D13" s="9">
         <f>D10+D11+D12</f>
